--- a/testplan/testplan.xlsx
+++ b/testplan/testplan.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\SV\apb_protocol_UVM_tb\testplan\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D2FA687C-62D9-4B77-94DE-CE94112FDEBD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{237987E0-FB21-497F-9E51-D26E61EB68CF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="70" uniqueCount="40">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="70" uniqueCount="38">
   <si>
     <t>Директория</t>
   </si>
@@ -58,9 +58,6 @@
   </si>
   <si>
     <t>README.md</t>
-  </si>
-  <si>
-    <t>-</t>
   </si>
   <si>
     <t>single_write_slave2_test</t>
@@ -155,9 +152,6 @@
   <si>
     <t>1) Сброс
 2) Подавать случайные операции со случайными задержками</t>
-  </si>
-  <si>
-    <t>В разработке</t>
   </si>
   <si>
     <t>back_to_back_write_test</t>
@@ -651,13 +645,13 @@
         <v>10</v>
       </c>
       <c r="E2" s="12" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="F2" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="G2" s="2" t="s">
         <v>31</v>
-      </c>
-      <c r="G2" s="2" t="s">
-        <v>32</v>
       </c>
     </row>
     <row r="3" spans="1:7" ht="75" x14ac:dyDescent="0.25">
@@ -665,22 +659,22 @@
         <v>7</v>
       </c>
       <c r="B3" s="11" t="s">
+        <v>11</v>
+      </c>
+      <c r="C3" s="12" t="s">
         <v>12</v>
-      </c>
-      <c r="C3" s="12" t="s">
-        <v>13</v>
       </c>
       <c r="D3" s="2" t="s">
         <v>10</v>
       </c>
       <c r="E3" s="12" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="F3" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="G3" s="2" t="s">
         <v>31</v>
-      </c>
-      <c r="G3" s="2" t="s">
-        <v>32</v>
       </c>
     </row>
     <row r="4" spans="1:7" ht="112.5" x14ac:dyDescent="0.25">
@@ -688,22 +682,22 @@
         <v>7</v>
       </c>
       <c r="B4" s="11" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C4" s="12" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="D4" s="2" t="s">
         <v>10</v>
       </c>
       <c r="E4" s="12" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="F4" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="G4" s="2" t="s">
         <v>31</v>
-      </c>
-      <c r="G4" s="2" t="s">
-        <v>32</v>
       </c>
     </row>
     <row r="5" spans="1:7" ht="112.5" x14ac:dyDescent="0.25">
@@ -711,22 +705,22 @@
         <v>7</v>
       </c>
       <c r="B5" s="11" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C5" s="12" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="D5" s="2" t="s">
         <v>10</v>
       </c>
       <c r="E5" s="12" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="F5" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="G5" s="2" t="s">
         <v>31</v>
-      </c>
-      <c r="G5" s="2" t="s">
-        <v>32</v>
       </c>
     </row>
     <row r="6" spans="1:7" ht="112.5" x14ac:dyDescent="0.25">
@@ -734,22 +728,22 @@
         <v>7</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="D6" s="2" t="s">
         <v>10</v>
       </c>
       <c r="E6" s="12" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="F6" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="G6" s="2" t="s">
         <v>31</v>
-      </c>
-      <c r="G6" s="2" t="s">
-        <v>32</v>
       </c>
     </row>
     <row r="7" spans="1:7" ht="112.5" x14ac:dyDescent="0.25">
@@ -757,22 +751,22 @@
         <v>7</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="D7" s="2" t="s">
         <v>10</v>
       </c>
       <c r="E7" s="12" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="F7" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="G7" s="2" t="s">
         <v>31</v>
-      </c>
-      <c r="G7" s="2" t="s">
-        <v>32</v>
       </c>
     </row>
     <row r="8" spans="1:7" ht="112.5" x14ac:dyDescent="0.25">
@@ -780,22 +774,22 @@
         <v>7</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="D8" s="2" t="s">
         <v>10</v>
       </c>
       <c r="E8" s="12" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="F8" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="G8" s="2" t="s">
         <v>31</v>
-      </c>
-      <c r="G8" s="2" t="s">
-        <v>32</v>
       </c>
     </row>
     <row r="9" spans="1:7" ht="56.25" x14ac:dyDescent="0.25">
@@ -803,22 +797,22 @@
         <v>7</v>
       </c>
       <c r="B9" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="C9" s="2" t="s">
         <v>28</v>
-      </c>
-      <c r="C9" s="2" t="s">
-        <v>29</v>
       </c>
       <c r="D9" s="2" t="s">
         <v>10</v>
       </c>
       <c r="E9" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="F9" s="2" t="s">
         <v>30</v>
       </c>
-      <c r="F9" s="2" t="s">
-        <v>36</v>
-      </c>
       <c r="G9" s="2" t="s">
-        <v>11</v>
+        <v>31</v>
       </c>
     </row>
     <row r="10" spans="1:7" ht="56.25" x14ac:dyDescent="0.25">
@@ -826,22 +820,22 @@
         <v>7</v>
       </c>
       <c r="B10" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="C10" s="2" t="s">
         <v>33</v>
-      </c>
-      <c r="C10" s="2" t="s">
-        <v>34</v>
       </c>
       <c r="D10" s="2" t="s">
         <v>10</v>
       </c>
       <c r="E10" s="2" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="F10" s="2" t="s">
-        <v>36</v>
+        <v>30</v>
       </c>
       <c r="G10" s="2" t="s">
-        <v>11</v>
+        <v>31</v>
       </c>
     </row>
     <row r="13" spans="1:7" ht="18.75" x14ac:dyDescent="0.25">

--- a/testplan/testplan.xlsx
+++ b/testplan/testplan.xlsx
@@ -8,12 +8,13 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\SV\apb_protocol_UVM_tb\testplan\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{237987E0-FB21-497F-9E51-D26E61EB68CF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F1AA9A8E-447E-49E5-B2BC-B663E13B0BAE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="master_tp" sheetId="1" r:id="rId1"/>
+    <sheet name="slave_tp" sheetId="2" r:id="rId2"/>
   </sheets>
   <calcPr calcId="162913"/>
   <extLst>
@@ -25,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="70" uniqueCount="38">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="126" uniqueCount="61">
   <si>
     <t>Директория</t>
   </si>
@@ -144,9 +145,6 @@
     <t>Успешно выполнен</t>
   </si>
   <si>
-    <t>full_session_test</t>
-  </si>
-  <si>
     <t>Проверка всех функций за одну сессию</t>
   </si>
   <si>
@@ -161,6 +159,92 @@
   </si>
   <si>
     <t>back_to_back_rw_test</t>
+  </si>
+  <si>
+    <t>tb/tests/apb_slave_tests</t>
+  </si>
+  <si>
+    <t>В разработке</t>
+  </si>
+  <si>
+    <t>-</t>
+  </si>
+  <si>
+    <t>single_valid_write_test</t>
+  </si>
+  <si>
+    <t>Проверка одиночной записи по допустимому адресу</t>
+  </si>
+  <si>
+    <t>1) Сброс
+2) Подать: psel=1, penable=1, pwrite=1, paddr&lt;128, pwdata
+3) Проверить: pready=1, pslverr=0, memory[paddr] == pwdata</t>
+  </si>
+  <si>
+    <t>single_valid_read_test</t>
+  </si>
+  <si>
+    <t>Проверка одиночного чтения по допустимому адресу</t>
+  </si>
+  <si>
+    <t>single_invalid_write_test</t>
+  </si>
+  <si>
+    <t>1) Сброс
+2) Записать значение по разрешенному адресу
+3) Подать: psel=1, penable=1, pwrite=0, paddr
+4) Проверить: pready=1, pslverr=0, prdata == memory[paddr]</t>
+  </si>
+  <si>
+    <t>1) Сброс
+2) Подать: psel=1, penable=1, pwrite=1, paddr&gt;128, pwdata
+3) Проверить: pready=1, pslverr=1, memory[paddr] == old_value</t>
+  </si>
+  <si>
+    <t>single_invalid_read_test</t>
+  </si>
+  <si>
+    <t>Проверка выставления сигнала ошибки при попытке записи по запрещенному адресу</t>
+  </si>
+  <si>
+    <t>Проверка выставления сигнала ошибки при попытке чтения из запрещенного адреса</t>
+  </si>
+  <si>
+    <t>1) Сброс
+2) Подать: psel=1, penable=1, pwrite=0, paddr&gt;128
+3) Проверить: pready=1, pslverr=1, prdata == 0</t>
+  </si>
+  <si>
+    <t>no_psel_test</t>
+  </si>
+  <si>
+    <t>Проверка игнорирования сигналов при psel=0</t>
+  </si>
+  <si>
+    <t>1) Сброс
+2) Подать: psel=0, penable=1, pwrite, paddr, pwdata
+3) Проверить: pready=0, pslverr=0</t>
+  </si>
+  <si>
+    <t>no_penable_test</t>
+  </si>
+  <si>
+    <t>Проверка игнорирования сигналов при penable=0</t>
+  </si>
+  <si>
+    <t>1) Сброс
+2) Подать: psel=1, penable=0, pwrite, paddr, pwdata
+3) Проверить: pready=0, pslverr=0</t>
+  </si>
+  <si>
+    <t>full_slave_session_test</t>
+  </si>
+  <si>
+    <t>1) Сброс
+2) Подать случайные операции</t>
+  </si>
+  <si>
+    <t>full_master_session_test</t>
   </si>
 </sst>
 </file>
@@ -728,7 +812,7 @@
         <v>7</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="C6" s="2" t="s">
         <v>21</v>
@@ -751,7 +835,7 @@
         <v>7</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C7" s="2" t="s">
         <v>23</v>
@@ -774,7 +858,7 @@
         <v>7</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="C8" s="2" t="s">
         <v>25</v>
@@ -820,16 +904,16 @@
         <v>7</v>
       </c>
       <c r="B10" s="2" t="s">
+        <v>60</v>
+      </c>
+      <c r="C10" s="2" t="s">
         <v>32</v>
       </c>
-      <c r="C10" s="2" t="s">
+      <c r="D10" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="E10" s="2" t="s">
         <v>33</v>
-      </c>
-      <c r="D10" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="E10" s="2" t="s">
-        <v>34</v>
       </c>
       <c r="F10" s="2" t="s">
         <v>30</v>
@@ -1005,4 +1089,207 @@
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="1200" verticalDpi="1200" r:id="rId1"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9194C7C8-FE7F-4455-9140-E8AA2E93A071}">
+  <dimension ref="A1:G8"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="30.140625" customWidth="1"/>
+    <col min="2" max="2" width="27.140625" customWidth="1"/>
+    <col min="3" max="3" width="30.28515625" customWidth="1"/>
+    <col min="4" max="4" width="22.140625" customWidth="1"/>
+    <col min="5" max="5" width="64.42578125" customWidth="1"/>
+    <col min="6" max="6" width="27.42578125" customWidth="1"/>
+    <col min="7" max="7" width="34.7109375" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:7" ht="40.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="2" spans="1:7" ht="93.75" x14ac:dyDescent="0.25">
+      <c r="A2" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="B2" s="11" t="s">
+        <v>40</v>
+      </c>
+      <c r="C2" s="12" t="s">
+        <v>41</v>
+      </c>
+      <c r="D2" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="E2" s="12" t="s">
+        <v>42</v>
+      </c>
+      <c r="F2" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="G2" s="2" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7" ht="93.75" x14ac:dyDescent="0.25">
+      <c r="A3" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="B3" s="11" t="s">
+        <v>43</v>
+      </c>
+      <c r="C3" s="12" t="s">
+        <v>44</v>
+      </c>
+      <c r="D3" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="E3" s="12" t="s">
+        <v>46</v>
+      </c>
+      <c r="F3" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="G3" s="2" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7" ht="93.75" x14ac:dyDescent="0.25">
+      <c r="A4" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="B4" s="11" t="s">
+        <v>45</v>
+      </c>
+      <c r="C4" s="12" t="s">
+        <v>49</v>
+      </c>
+      <c r="D4" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="E4" s="12" t="s">
+        <v>47</v>
+      </c>
+      <c r="F4" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="G4" s="2" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7" ht="75" x14ac:dyDescent="0.25">
+      <c r="A5" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="B5" s="11" t="s">
+        <v>48</v>
+      </c>
+      <c r="C5" s="12" t="s">
+        <v>50</v>
+      </c>
+      <c r="D5" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="E5" s="12" t="s">
+        <v>51</v>
+      </c>
+      <c r="F5" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="G5" s="2" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7" ht="56.25" x14ac:dyDescent="0.25">
+      <c r="A6" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="B6" s="11" t="s">
+        <v>52</v>
+      </c>
+      <c r="C6" s="12" t="s">
+        <v>53</v>
+      </c>
+      <c r="D6" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="E6" s="12" t="s">
+        <v>54</v>
+      </c>
+      <c r="F6" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="G6" s="2" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7" ht="56.25" x14ac:dyDescent="0.25">
+      <c r="A7" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="B7" s="11" t="s">
+        <v>55</v>
+      </c>
+      <c r="C7" s="12" t="s">
+        <v>56</v>
+      </c>
+      <c r="D7" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="E7" s="12" t="s">
+        <v>57</v>
+      </c>
+      <c r="F7" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="G7" s="2" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7" ht="37.5" x14ac:dyDescent="0.25">
+      <c r="A8" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="B8" s="11" t="s">
+        <v>58</v>
+      </c>
+      <c r="C8" s="12" t="s">
+        <v>32</v>
+      </c>
+      <c r="D8" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="E8" s="12" t="s">
+        <v>59</v>
+      </c>
+      <c r="F8" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="G8" s="2" t="s">
+        <v>39</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>